--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487567_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487567_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1454</v>
+        <v>5.7132</v>
       </c>
       <c r="E2" t="n">
-        <v>9.6547</v>
+        <v>5.1849</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4907</v>
+        <v>0.5284</v>
       </c>
       <c r="G2" t="n">
         <v>-0.3363</v>
@@ -610,13 +610,13 @@
         <v>1.9585</v>
       </c>
       <c r="S2" t="n">
-        <v>9.523199999999999</v>
+        <v>4.0911</v>
       </c>
       <c r="T2" t="n">
-        <v>6.713</v>
+        <v>2.2431</v>
       </c>
       <c r="U2" t="n">
-        <v>2.8102</v>
+        <v>1.8479</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1984</v>
+        <v>1.8262</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5293</v>
+        <v>1.8363</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3309</v>
+        <v>-0.0101</v>
       </c>
       <c r="G3" t="n">
         <v>2.0263</v>
@@ -688,13 +688,13 @@
         <v>0.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6113</v>
+        <v>0.0165</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1429</v>
+        <v>0.1641</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4684</v>
+        <v>-0.1476</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6083</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.286</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.74</v>
+        <v>-0.9478</v>
       </c>
       <c r="F4" t="n">
-        <v>2.026</v>
+        <v>1.8122</v>
       </c>
       <c r="G4" t="n">
         <v>-1.0145</v>
@@ -766,13 +766,13 @@
         <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.112</v>
+        <v>0.4664</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6599</v>
+        <v>0.1323</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.3341</v>
       </c>
       <c r="V4" t="n">
         <v>1.2166</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. SANJURJO BOTEJARA</t>
+          <t>R. ESPINOZA OROZCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1816</v>
+        <v>0.4097</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0542</v>
+        <v>1.2031</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2358</v>
+        <v>-0.7934</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4586</v>
+        <v>-2.0723</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9885</v>
+        <v>-1.6374</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4701</v>
+        <v>-0.4349</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3722</v>
+        <v>-0.0015</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6447000000000001</v>
+        <v>-0.3489</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7275</v>
+        <v>0.3474</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0864</v>
+        <v>-2.0708</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3437</v>
+        <v>-1.2884</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2573</v>
+        <v>-0.7823</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7834</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1958</v>
+        <v>1.5668</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5814</v>
+        <v>0.9266</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3388</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2427</v>
+        <v>0.9272</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2754</v>
+        <v>2.9263</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>4.1429</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. ESPINOZA OROZCO</t>
+          <t>P. SANJURJO BOTEJARA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4256</v>
+        <v>0.194</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3649</v>
+        <v>0.2159</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0607</v>
+        <v>-0.0219</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.0723</v>
+        <v>1.4586</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6374</v>
+        <v>0.9885</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4349</v>
+        <v>0.4701</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0015</v>
+        <v>1.3722</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3489</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3474</v>
+        <v>0.7275</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0708</v>
+        <v>0.0864</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2884</v>
+        <v>0.3437</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7823</v>
+        <v>-0.2573</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3709</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5668</v>
+        <v>0.1958</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9087</v>
+        <v>-0.2058</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5686</v>
+        <v>-0.177</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6599</v>
+        <v>-0.0288</v>
       </c>
       <c r="V6" t="n">
-        <v>2.9263</v>
+        <v>-0.2754</v>
       </c>
       <c r="W6" t="n">
-        <v>4.1429</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1362</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.7029</v>
+        <v>-2.6631</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5667</v>
+        <v>1.7271</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1464</v>
@@ -1000,13 +1000,13 @@
         <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.08890000000000001</v>
+        <v>1.1113</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5411</v>
+        <v>0.4987</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4522</v>
+        <v>0.6125</v>
       </c>
       <c r="V7" t="n">
         <v>0.6659</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.311</v>
+        <v>-1.1875</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4674</v>
+        <v>-1.7181</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1564</v>
+        <v>0.5306</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0193</v>
@@ -1078,13 +1078,13 @@
         <v>1.7626</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0187</v>
+        <v>1.1048</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.6816</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0489</v>
+        <v>0.4232</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0564</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0134</v>
+        <v>-4.0075</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1139</v>
+        <v>-2.0545</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8995</v>
+        <v>-1.9529</v>
       </c>
       <c r="G9" t="n">
         <v>-3.13</v>
@@ -1156,13 +1156,13 @@
         <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>0.059</v>
+        <v>0.065</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0465</v>
+        <v>0.1059</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0126</v>
+        <v>-0.0409</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5507</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0753</v>
+        <v>-4.2018</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1212</v>
+        <v>-3.1408</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.954</v>
+        <v>-1.061</v>
       </c>
       <c r="G10" t="n">
         <v>-4.5884</v>
@@ -1234,13 +1234,13 @@
         <v>0.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0536</v>
+        <v>0.8199</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8734</v>
+        <v>0.107</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8197</v>
+        <v>0.7128</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2166</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.513299999999999</v>
+        <v>-1.325300000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2721</v>
+        <v>-2.084099999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7588999999999999</v>
+        <v>0.7590000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-10.8223</v>
@@ -1303,25 +1303,25 @@
         <v>-4.5421</v>
       </c>
       <c r="P11" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="Q11" t="n">
-        <v>-9.792199999999999</v>
+        <v>-9.792200000000001</v>
       </c>
       <c r="R11" t="n">
         <v>9.792300000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>7.207599999999998</v>
+        <v>8.395799999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5672</v>
+        <v>3.7551</v>
       </c>
       <c r="U11" t="n">
-        <v>4.6403</v>
+        <v>4.6404</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1014</v>
+        <v>1.101400000000001</v>
       </c>
       <c r="W11" t="n">
         <v>8.228299999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.7212</v>
+        <v>4.1527</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1897</v>
+        <v>2.292</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5316</v>
+        <v>1.8607</v>
       </c>
       <c r="G12" t="n">
         <v>3.3339</v>
@@ -1390,13 +1390,13 @@
         <v>1.3709</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6345</v>
+        <v>-0.2031</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.904</v>
+        <v>-0.8016</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2694</v>
+        <v>0.5986</v>
       </c>
       <c r="V12" t="n">
         <v>0.8260999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4237</v>
+        <v>1.9012</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1536</v>
+        <v>2.3583</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.73</v>
+        <v>-0.4571</v>
       </c>
       <c r="G13" t="n">
         <v>1.6789</v>
@@ -1468,13 +1468,13 @@
         <v>0.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6469</v>
+        <v>-0.1694</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3982</v>
+        <v>-0.1935</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2488</v>
+        <v>0.0241</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MUÑOZ</t>
+          <t>J. FERNANDEZ PILLADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0537</v>
+        <v>1.1448</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9354</v>
+        <v>-0.6694</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9891</v>
+        <v>1.8142</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0012</v>
+        <v>1.9398</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8844</v>
+        <v>2.5356</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1168</v>
+        <v>-0.5958</v>
       </c>
       <c r="J14" t="n">
-        <v>0.541</v>
+        <v>0.7514</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0616</v>
+        <v>2.5961</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5206</v>
+        <v>-1.8446</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4602</v>
+        <v>1.1884</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8228</v>
+        <v>-0.0604</v>
       </c>
       <c r="O14" t="n">
-        <v>1.6374</v>
+        <v>1.2488</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9792</v>
+        <v>0.1958</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9585</v>
+        <v>-1.1751</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6929</v>
+        <v>-0.9909</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0098</v>
+        <v>-0.5211</v>
       </c>
       <c r="U14" t="n">
-        <v>0.317</v>
+        <v>-0.4698</v>
       </c>
       <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="X14" t="n">
         <v>-0.2754</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.492</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-1.7673</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. GIL REY</t>
+          <t>I. FERNANDEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.7358</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5295</v>
+        <v>-0.9354</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1328</v>
+        <v>1.6711</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5284</v>
+        <v>3.0012</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9024</v>
+        <v>1.8844</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4308</v>
+        <v>1.1168</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0016</v>
+        <v>0.541</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7743</v>
+        <v>1.0616</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7727000000000001</v>
+        <v>-0.5206</v>
       </c>
       <c r="M15" t="n">
-        <v>1.53</v>
+        <v>2.4602</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1281</v>
+        <v>0.8228</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6581</v>
+        <v>1.6374</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5668</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.1336</v>
+        <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5668</v>
+        <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.575</v>
+        <v>-1.0109</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1029</v>
+        <v>-1.0098</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.472</v>
+        <v>-0.001</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2166</v>
+        <v>-0.2754</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7086</v>
+        <v>1.492</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.492</v>
+        <v>-1.7673</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ PILLADO</t>
+          <t>C. GIL REY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1298</v>
+        <v>0.5498</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8741</v>
+        <v>-0.9389</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0039</v>
+        <v>1.4887</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9398</v>
+        <v>1.5284</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5356</v>
+        <v>-0.9024</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5958</v>
+        <v>2.4308</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7514</v>
+        <v>-0.0016</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5961</v>
+        <v>-0.7743</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.8446</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1884</v>
+        <v>1.53</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0604</v>
+        <v>-0.1281</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2488</v>
+        <v>1.6581</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1958</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1751</v>
+        <v>-3.1336</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3709</v>
+        <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.0058</v>
+        <v>-0.6284</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7258</v>
+        <v>-0.5123</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2801</v>
+        <v>-0.1161</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2754</v>
+        <v>2.7086</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.263</v>
+        <v>0.4607</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0297</v>
+        <v>1.2344</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2927</v>
+        <v>-0.7736</v>
       </c>
       <c r="G17" t="n">
         <v>2.1972</v>
@@ -1780,13 +1780,13 @@
         <v>1.7626</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6134</v>
+        <v>-0.8897</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9634</v>
+        <v>-0.7587</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6501</v>
+        <v>-0.131</v>
       </c>
       <c r="V17" t="n">
         <v>-1.4344</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BLANCO BLANCO</t>
+          <t>S. LOPE REBOLLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5653</v>
+        <v>-1.6774</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.386</v>
+        <v>-2.0292</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1794</v>
+        <v>0.3518</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7126</v>
+        <v>-1.1445</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.5261</v>
+        <v>-0.6747</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8135</v>
+        <v>-0.4698</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1772</v>
+        <v>-0.6288</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3032</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1261</v>
+        <v>0.0501</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5354</v>
+        <v>-0.5157</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2228</v>
+        <v>0.0042</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6874</v>
+        <v>-0.5198</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1899</v>
+        <v>-0.3163</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2088</v>
+        <v>-0.2253</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3987</v>
+        <v>-0.091</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.6083</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. LOPE REBOLLO</t>
+          <t>A. BLANCO BLANCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.59</v>
+        <v>-2.0253</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1315</v>
+        <v>-1.7953</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4585</v>
+        <v>-0.23</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1445</v>
+        <v>-1.7126</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6747</v>
+        <v>-2.5261</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4698</v>
+        <v>0.8135</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6288</v>
+        <v>-1.1772</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-1.3032</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0501</v>
+        <v>0.1261</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5157</v>
+        <v>-0.5354</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0042</v>
+        <v>-1.2228</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5198</v>
+        <v>0.6874</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5668</v>
+        <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2289</v>
+        <v>-0.2701</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3276</v>
+        <v>-0.6181</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9013</v>
+        <v>0.348</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6083</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6083</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1969,19 +1969,19 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.5134</v>
+        <v>5.2423</v>
       </c>
       <c r="E20" t="n">
         <v>-0.4834999999999998</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9968</v>
+        <v>5.7258</v>
       </c>
       <c r="G20" t="n">
         <v>10.8223</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3542</v>
+        <v>-1.354200000000001</v>
       </c>
       <c r="I20" t="n">
         <v>12.1764</v>
@@ -2005,7 +2005,7 @@
         <v>7.6343</v>
       </c>
       <c r="P20" t="n">
-        <v>-9.999999999976694e-05</v>
+        <v>-9.999999999987796e-05</v>
       </c>
       <c r="Q20" t="n">
         <v>-9.7925</v>
@@ -2014,19 +2014,19 @@
         <v>9.792300000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>-7.2075</v>
+        <v>-4.4788</v>
       </c>
       <c r="T20" t="n">
-        <v>-4.6405</v>
+        <v>-4.6404</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.5672</v>
+        <v>0.1618000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>-1.1015</v>
       </c>
       <c r="W20" t="n">
-        <v>7.402299999999999</v>
+        <v>7.4023</v>
       </c>
       <c r="X20" t="n">
         <v>-8.5038</v>
